--- a/data/trans_bre/P57_AC_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 7,61</t>
+          <t>0,4; 7,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,43</t>
+          <t>1,65; 9,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,63</t>
+          <t>2,37; 9,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 8,18</t>
+          <t>-0,96; 8,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 10,67</t>
+          <t>0,52; 10,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 13,91</t>
+          <t>2,22; 13,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 12,5</t>
+          <t>2,92; 12,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 12,98</t>
+          <t>-1,36; 13,35</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,32</t>
+          <t>-0,56; 6,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,73</t>
+          <t>4,97; 11,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,15</t>
+          <t>0,42; 5,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 22,7</t>
+          <t>-3,02; 22,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 10,13</t>
+          <t>-0,83; 9,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 18,57</t>
+          <t>7,43; 18,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,46</t>
+          <t>0,44; 6,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 57,38</t>
+          <t>-5,13; 55,91</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 1,5</t>
+          <t>-10,24; 1,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 7,79</t>
+          <t>-5,73; 6,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 4,51</t>
+          <t>-6,58; 4,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 1,63</t>
+          <t>-9,02; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 2,42</t>
+          <t>-14,82; 2,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 13,47</t>
+          <t>-8,77; 11,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 6,28</t>
+          <t>-8,69; 6,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 3,25</t>
+          <t>-14,57; 3,58</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,21</t>
+          <t>0,45; 5,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 9,06</t>
+          <t>4,58; 9,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,12</t>
+          <t>1,18; 5,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 17,14</t>
+          <t>-1,56; 19,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,84</t>
+          <t>0,64; 7,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 13,96</t>
+          <t>6,77; 14,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,56</t>
+          <t>1,45; 6,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 38,6</t>
+          <t>-2,53; 45,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AC_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>4,72</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 7,47</t>
+          <t>0,45; 7,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,35</t>
+          <t>1,23; 9,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,64</t>
+          <t>1,92; 9,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 8,28</t>
+          <t>0,1; 9,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 10,35</t>
+          <t>0,58; 10,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 13,54</t>
+          <t>1,79; 13,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 12,41</t>
+          <t>2,35; 12,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 13,35</t>
+          <t>0,05; 14,93</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 6,15</t>
+          <t>-0,54; 6,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,68</t>
+          <t>5,25; 11,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,18</t>
+          <t>0,21; 5,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 22,63</t>
+          <t>-1,24; 4,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 9,84</t>
+          <t>-0,83; 9,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 18,37</t>
+          <t>8,01; 18,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,49</t>
+          <t>0,24; 6,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 55,91</t>
+          <t>-1,96; 7,87</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,7</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-6,35%</t>
+          <t>-6,04%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 1,55</t>
+          <t>-10,3; 1,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 6,84</t>
+          <t>-5,54; 8,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 4,43</t>
+          <t>-6,55; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 1,94</t>
+          <t>-9,3; 1,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 2,36</t>
+          <t>-14,79; 2,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 11,29</t>
+          <t>-8,33; 13,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 6,22</t>
+          <t>-8,54; 5,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 3,58</t>
+          <t>-14,76; 3,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,05</t>
+          <t>0,62; 5,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,13</t>
+          <t>4,64; 9,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,23</t>
+          <t>1,03; 4,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 19,39</t>
+          <t>-1,0; 3,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,51</t>
+          <t>0,91; 7,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 14,15</t>
+          <t>6,88; 14,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,72</t>
+          <t>1,29; 6,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 45,06</t>
+          <t>-1,51; 6,2</t>
         </is>
       </c>
     </row>
